--- a/artfynd/A 36227-2024 artfynd.xlsx
+++ b/artfynd/A 36227-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88855052</v>
+        <v>56146586</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1853</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,21 +710,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Rödån, Vg</t>
+          <t>Hökensås Ö Rödsjön, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448646.5779622511</v>
+        <v>448726</v>
       </c>
       <c r="R2" t="n">
-        <v>6434054.342987608</v>
+        <v>6434285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-12-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-12-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,60 +765,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Johan Rova</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
-        </is>
-      </c>
+          <t>Johan Rova</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88855055</v>
+        <v>99410137</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>1853</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,26 +816,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Rödån, Vg</t>
+          <t>Hökensås Ö Rödsjön, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448639.256150918</v>
+        <v>448730</v>
       </c>
       <c r="R3" t="n">
-        <v>6434062.378043953</v>
+        <v>6434291</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skötselåtgärd inom ÅGP</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,19 +882,464 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>73695283</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5D, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>448606</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6434369</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>88855052</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söder om Rödån, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>448647</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6434054</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88855055</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Söder om Rödån, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>448639</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6434062</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>92535893</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bastabacken, Hökensås naturreservat, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448668</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6434150</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-04-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-04-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36227-2024 artfynd.xlsx
+++ b/artfynd/A 36227-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56146586</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99410137</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695283</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88855052</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88855055</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,8 +1370,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92535893</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>